--- a/resutls/chillgen.com/chillgen_20260907_01/qa/QA-20260907-AGENT-B036/SEO_QA_B036.xlsx
+++ b/resutls/chillgen.com/chillgen_20260907_01/qa/QA-20260907-AGENT-B036/SEO_QA_B036.xlsx
@@ -14,11 +14,11 @@
     <sheet name="QA_Issues" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'QA_Summary'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QA_Products'!$A$1:$S$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'QA_Summary'!$A$1:$C$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QA_Products'!$A$1:$T$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QA_Criteria'!$A$1:$J$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'QA_Images'!$A$1:$X$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'QA_Issues'!$A$1:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'QA_Issues'!$A$1:$K$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -618,61 +618,61 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Image_Audit rows visually checked via local B036 contact sheets and cross-checked with live gallery counts.</t>
+          <t>Image_Audit rows evaluated with evidence-driven rules over observation and alt fields; direct human visual confirmation remains a limitation.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>batch_status</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>QA_PASS</t>
-        </is>
+          <t>image_rows_in_scope</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>54</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>All products QA_PASS; QA_PASS is not APPROVED.</t>
+          <t>Image_Audit rows included in this batch scope.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>batch_average_final_score</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>95</v>
+          <t>batch_status</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>QA_FAIL</t>
+        </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Equal average of product final scores.</t>
+          <t>Evidence-driven rerun status; QA_PASS requires complete assessed weight, score &gt;=85, and no CRITICAL/MAJOR.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>qa_pass_count</t>
+          <t>batch_average_final_score</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>10</v>
+        <v>65.5</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Products meeting &gt;=85 with no CRITICAL/MAJOR.</t>
+          <t>Blank when any product has incomplete assessed weight.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>critical_count</t>
+          <t>qa_pass_count</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -680,14 +680,14 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>No critical issue found.</t>
+          <t>Products meeting &gt;=85 with no CRITICAL/MAJOR.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>major_count</t>
+          <t>critical_count</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -695,61 +695,93 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Auto MAJOR identity/non-slip findings were downgraded/resolved after live and image QA; remaining deployment constraints are limitations.</t>
+          <t>Products with at least one CRITICAL issue.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>limitation_count</t>
+          <t>major_count</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state and direct demand evidence limitations; do not block content QA but must be acknowledged before approval/deploy.</t>
+          <t>Total MAJOR issues from evidence-driven field/image checks.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>generated_at</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
-        </is>
+          <t>limitation_count</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>30</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>UTC timestamp.</t>
+          <t>Admin/export before-state, direct demand evidence, and visual-confirmation limitations.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>methodology_status</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>EVIDENCE_DRIVEN_RERUN_NO_FIXED_SCORE</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>No fixed FULL/100/95 scoring is used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>generated_at</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>UTC timestamp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>scope_note</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>QA covers B036 only; no workbook source edit, no approval, no Shopify deploy.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Operational boundary.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C18"/>
+  <autoFilter ref="A1:C20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -760,7 +792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -780,8 +812,9 @@
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
-    <col width="46" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="55" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -872,10 +905,15 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>limitation_count</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>issue_refs</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>evidence_refs</t>
         </is>
@@ -898,23 +936,23 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>95</v>
+        <v>65.5</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>95</v>
+        <v>65.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>95</v>
+        <v>65.5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>95</v>
+        <v>65.5</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_FAIL</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -940,17 +978,20 @@
         <v>0</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0001;LIM-0002</t>
-        </is>
+      <c r="R2" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0001;LIM-0002;LIM-0003;AUTO-0004;AUTO-0005;AUTO-0006</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>B036-351; live HTTP=200; local contact sheet</t>
         </is>
@@ -973,23 +1014,23 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_FAIL</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1015,17 +1056,20 @@
         <v>0</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0003;LIM-0004</t>
-        </is>
+      <c r="R3" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0007;LIM-0008;LIM-0009;AUTO-0010;AUTO-0011;AUTO-0012</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>B036-352; live HTTP=200; local contact sheet</t>
         </is>
@@ -1048,23 +1092,23 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>95</v>
+        <v>65.5</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>95</v>
+        <v>65.5</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>95</v>
+        <v>65.5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>95</v>
+        <v>65.5</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_FAIL</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1090,17 +1134,20 @@
         <v>0</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0005;LIM-0006</t>
-        </is>
+      <c r="R4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0013;LIM-0014;LIM-0015;AUTO-0016;AUTO-0017;AUTO-0018</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>B036-353; live HTTP=200; local contact sheet</t>
         </is>
@@ -1123,23 +1170,23 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_REVISE</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1165,17 +1212,20 @@
         <v>0</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0007;LIM-0008</t>
-        </is>
+      <c r="R5" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0019;LIM-0020;LIM-0021;AUTO-0022</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>B036-354; live HTTP=200; local contact sheet</t>
         </is>
@@ -1198,23 +1248,23 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_FAIL</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1240,17 +1290,20 @@
         <v>0</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0009;LIM-0010</t>
-        </is>
+      <c r="R6" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0023;LIM-0024;LIM-0025;AUTO-0026;AUTO-0027;AUTO-0028</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>B036-355; live HTTP=200; local contact sheet</t>
         </is>
@@ -1273,23 +1326,23 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_FAIL</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1315,17 +1368,20 @@
         <v>0</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0011;LIM-0012</t>
-        </is>
+      <c r="R7" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0029;LIM-0030;LIM-0031;AUTO-0032;AUTO-0033;AUTO-0034</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>B036-356; live HTTP=200; local contact sheet</t>
         </is>
@@ -1348,23 +1404,23 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>95</v>
+        <v>65.5</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>95</v>
+        <v>65.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>95</v>
+        <v>65.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>95</v>
+        <v>65.5</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_FAIL</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1390,17 +1446,20 @@
         <v>0</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0013;LIM-0014</t>
-        </is>
+      <c r="R8" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0035;LIM-0036;LIM-0037;AUTO-0038;AUTO-0039;AUTO-0040</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>B036-357; live HTTP=200; local contact sheet</t>
         </is>
@@ -1423,23 +1482,23 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_FAIL</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1465,17 +1524,20 @@
         <v>0</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0015;LIM-0016</t>
-        </is>
+      <c r="R9" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0041;LIM-0042;LIM-0043;AUTO-0044;AUTO-0045;AUTO-0046</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>B036-358; live HTTP=200; local contact sheet</t>
         </is>
@@ -1498,23 +1560,23 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_REVISE</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1540,17 +1602,20 @@
         <v>0</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0017;LIM-0018</t>
-        </is>
+      <c r="R10" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0047;LIM-0048;LIM-0049;AUTO-0050</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>B036-359; live HTTP=200; local contact sheet</t>
         </is>
@@ -1573,23 +1638,23 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_FAIL</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1615,24 +1680,27 @@
         <v>0</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0019;LIM-0020</t>
-        </is>
+      <c r="R11" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
+          <t>LIM-0051;LIM-0052;LIM-0053;AUTO-0054;AUTO-0055;AUTO-0056</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
           <t>B036-360; live HTTP=200; local contact sheet</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S11"/>
+  <autoFilter ref="A1:T11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
@@ -1667,7 +1735,7 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1752,7 +1820,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -1778,21 +1846,21 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -1832,7 +1900,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1872,7 +1940,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1898,21 +1966,21 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1922,7 +1990,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>LIM-0001;LIM-0002</t>
+          <t>LIM-0001;LIM-0002;LIM-0003;AUTO-0004;AUTO-0005;AUTO-0006</t>
         </is>
       </c>
     </row>
@@ -1942,21 +2010,21 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Title length 24 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1982,21 +2050,21 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Title length 24 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2036,7 +2104,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 126; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2076,7 +2144,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 90 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2094,29 +2162,29 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B036 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2124,7 +2192,11 @@
           <t>B036-351; live=https://chillgen.com/products/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0001;LIM-0002;LIM-0003;AUTO-0004;AUTO-0005;AUTO-0006</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2134,29 +2206,29 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B036 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2166,7 +2238,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>LIM-0001;LIM-0002</t>
+          <t>LIM-0001;LIM-0002;LIM-0003;AUTO-0004;AUTO-0005;AUTO-0006</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2272,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2226,21 +2298,21 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2280,7 +2352,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2320,7 +2392,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2346,21 +2418,21 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2370,7 +2442,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>LIM-0003;LIM-0004</t>
+          <t>LIM-0007;LIM-0008;LIM-0009;AUTO-0010;AUTO-0011;AUTO-0012</t>
         </is>
       </c>
     </row>
@@ -2390,21 +2462,21 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Title length 21 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2430,21 +2502,21 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Title length 21 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2470,21 +2542,21 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 117; product specificity is acceptable but borderline.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2524,7 +2596,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 78 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2542,29 +2614,29 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B036 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2572,7 +2644,11 @@
           <t>B036-352; live=https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0007;LIM-0008;LIM-0009;AUTO-0010;AUTO-0011;AUTO-0012</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2582,29 +2658,29 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B036 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2614,7 +2690,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>LIM-0003;LIM-0004</t>
+          <t>LIM-0007;LIM-0008;LIM-0009;AUTO-0010;AUTO-0011;AUTO-0012</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2724,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2674,21 +2750,21 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2728,7 +2804,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2768,7 +2844,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2794,21 +2870,21 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2818,7 +2894,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>LIM-0005;LIM-0006</t>
+          <t>LIM-0013;LIM-0014;LIM-0015;AUTO-0016;AUTO-0017;AUTO-0018</t>
         </is>
       </c>
     </row>
@@ -2838,21 +2914,21 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Title length 23 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2878,21 +2954,21 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Title length 23 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2932,7 +3008,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 122; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2972,7 +3048,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 85 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2990,29 +3066,29 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B036 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -3020,7 +3096,11 @@
           <t>B036-353; live=https://chillgen.com/products/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0013;LIM-0014;LIM-0015;AUTO-0016;AUTO-0017;AUTO-0018</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3030,29 +3110,29 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B036 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -3062,7 +3142,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>LIM-0005;LIM-0006</t>
+          <t>LIM-0013;LIM-0014;LIM-0015;AUTO-0016;AUTO-0017;AUTO-0018</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3176,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -3122,21 +3202,21 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -3176,7 +3256,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -3216,7 +3296,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -3242,21 +3322,21 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -3266,7 +3346,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>LIM-0007;LIM-0008</t>
+          <t>LIM-0019;LIM-0020;LIM-0021;AUTO-0022</t>
         </is>
       </c>
     </row>
@@ -3286,21 +3366,21 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 25, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -3326,21 +3406,21 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 25, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -3380,7 +3460,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 124; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -3420,7 +3500,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 81 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -3438,29 +3518,29 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B036 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -3468,7 +3548,11 @@
           <t>B036-354; live=https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0019;LIM-0020;LIM-0021;AUTO-0022</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3478,29 +3562,29 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B036 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -3510,7 +3594,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>LIM-0007;LIM-0008</t>
+          <t>LIM-0019;LIM-0020;LIM-0021;AUTO-0022</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3628,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -3570,21 +3654,21 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -3624,7 +3708,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -3664,7 +3748,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -3690,21 +3774,21 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -3714,7 +3798,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>LIM-0009;LIM-0010</t>
+          <t>LIM-0023;LIM-0024;LIM-0025;AUTO-0026;AUTO-0027;AUTO-0028</t>
         </is>
       </c>
     </row>
@@ -3734,21 +3818,21 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Title length 24 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -3774,21 +3858,21 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Title length 24 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3814,21 +3898,21 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 115; product specificity is acceptable but borderline.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -3868,7 +3952,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 82 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3886,29 +3970,29 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B036 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -3916,7 +4000,11 @@
           <t>B036-355; live=https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0023;LIM-0024;LIM-0025;AUTO-0026;AUTO-0027;AUTO-0028</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3926,29 +4014,29 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B036 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3958,7 +4046,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>LIM-0009;LIM-0010</t>
+          <t>LIM-0023;LIM-0024;LIM-0025;AUTO-0026;AUTO-0027;AUTO-0028</t>
         </is>
       </c>
     </row>
@@ -3992,7 +4080,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -4018,21 +4106,21 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -4072,7 +4160,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -4112,7 +4200,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -4138,21 +4226,21 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -4162,7 +4250,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>LIM-0011;LIM-0012</t>
+          <t>LIM-0029;LIM-0030;LIM-0031;AUTO-0032;AUTO-0033;AUTO-0034</t>
         </is>
       </c>
     </row>
@@ -4182,21 +4270,21 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Title length 19 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -4222,21 +4310,21 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Title length 19 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -4262,21 +4350,21 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 108; product specificity is acceptable but borderline.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -4316,7 +4404,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 79 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -4334,29 +4422,29 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B036 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -4364,7 +4452,11 @@
           <t>B036-356; live=https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0029;LIM-0030;LIM-0031;AUTO-0032;AUTO-0033;AUTO-0034</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4374,29 +4466,29 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B036 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -4406,7 +4498,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>LIM-0011;LIM-0012</t>
+          <t>LIM-0029;LIM-0030;LIM-0031;AUTO-0032;AUTO-0033;AUTO-0034</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4532,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -4466,21 +4558,21 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -4520,7 +4612,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -4560,7 +4652,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -4586,21 +4678,21 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -4610,7 +4702,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>LIM-0013;LIM-0014</t>
+          <t>LIM-0035;LIM-0036;LIM-0037;AUTO-0038;AUTO-0039;AUTO-0040</t>
         </is>
       </c>
     </row>
@@ -4630,21 +4722,21 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Title length 22 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -4670,21 +4762,21 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Title length 22 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -4724,7 +4816,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 121; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -4764,7 +4856,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 79 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4782,29 +4874,29 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B036 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4812,7 +4904,11 @@
           <t>B036-357; live=https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0035;LIM-0036;LIM-0037;AUTO-0038;AUTO-0039;AUTO-0040</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4822,29 +4918,29 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B036 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4854,7 +4950,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>LIM-0013;LIM-0014</t>
+          <t>LIM-0035;LIM-0036;LIM-0037;AUTO-0038;AUTO-0039;AUTO-0040</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4984,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4914,21 +5010,21 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4968,7 +5064,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -5008,7 +5104,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -5034,21 +5130,21 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -5058,7 +5154,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>LIM-0015;LIM-0016</t>
+          <t>LIM-0041;LIM-0042;LIM-0043;AUTO-0044;AUTO-0045;AUTO-0046</t>
         </is>
       </c>
     </row>
@@ -5078,21 +5174,21 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Title length 21 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -5118,21 +5214,21 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Title length 21 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -5158,21 +5254,21 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 118; product specificity is acceptable but borderline.</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -5212,7 +5308,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 82 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -5230,29 +5326,29 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B036 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -5260,7 +5356,11 @@
           <t>B036-358; live=https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0041;LIM-0042;LIM-0043;AUTO-0044;AUTO-0045;AUTO-0046</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5270,29 +5370,29 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B036 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -5302,7 +5402,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>LIM-0015;LIM-0016</t>
+          <t>LIM-0041;LIM-0042;LIM-0043;AUTO-0044;AUTO-0045;AUTO-0046</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5436,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -5362,21 +5462,21 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -5416,7 +5516,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -5456,7 +5556,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -5482,21 +5582,21 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -5506,7 +5606,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>LIM-0017;LIM-0018</t>
+          <t>LIM-0047;LIM-0048;LIM-0049;AUTO-0050</t>
         </is>
       </c>
     </row>
@@ -5526,21 +5626,21 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 27, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -5566,21 +5666,21 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 27, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -5606,21 +5706,21 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 113; product specificity is acceptable but borderline.</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -5660,7 +5760,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 83 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -5678,29 +5778,29 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B036 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -5708,7 +5808,11 @@
           <t>B036-359; live=https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-e0ded989b1</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0047;LIM-0048;LIM-0049;AUTO-0050</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5718,29 +5822,29 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B036 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -5750,7 +5854,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>LIM-0017;LIM-0018</t>
+          <t>LIM-0047;LIM-0048;LIM-0049;AUTO-0050</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5888,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -5810,21 +5914,21 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5864,7 +5968,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5904,7 +6008,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -5930,21 +6034,21 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -5954,7 +6058,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>LIM-0019;LIM-0020</t>
+          <t>LIM-0051;LIM-0052;LIM-0053;AUTO-0054;AUTO-0055;AUTO-0056</t>
         </is>
       </c>
     </row>
@@ -5974,21 +6078,21 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Title length 24 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -6014,21 +6118,21 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Title length 24 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -6054,21 +6158,21 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G108" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 118; product specificity is acceptable but borderline.</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -6108,7 +6212,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 86 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -6126,29 +6230,29 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B036 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -6156,7 +6260,11 @@
           <t>B036-360; live=https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0051;LIM-0052;LIM-0053;AUTO-0054;AUTO-0055;AUTO-0056</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6166,29 +6274,29 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B036 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -6198,7 +6306,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>LIM-0019;LIM-0020</t>
+          <t>LIM-0051;LIM-0052;LIM-0053;AUTO-0054;AUTO-0055;AUTO-0056</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6332,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="53" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="43" customWidth="1" min="11" max="11"/>
@@ -6399,17 +6507,17 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: custom kids road map rug in classroom</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -6429,12 +6537,12 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -6448,24 +6556,24 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S2" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>B036-351; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_01.jpg</t>
+          <t>B036-351; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -6503,17 +6611,17 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: personalized road map rug size options</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -6533,12 +6641,12 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -6552,24 +6660,24 @@
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>B036-351; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_02.jpg</t>
+          <t>B036-351; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -6607,17 +6715,17 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: road map rug in classroom corner</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -6637,12 +6745,12 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6656,24 +6764,24 @@
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>B036-351; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_03.jpg</t>
+          <t>B036-351; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -6711,17 +6819,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: city road play rug in playroom</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -6741,12 +6849,12 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6760,24 +6868,24 @@
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>B036-351; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_04.jpg</t>
+          <t>B036-351; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -6815,17 +6923,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: road map classroom rug between tables</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -6845,12 +6953,12 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -6864,24 +6972,24 @@
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>B036-351; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_05.jpg</t>
+          <t>B036-351; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -6919,17 +7027,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: kids road map rug in bedroom play space</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -6949,12 +7057,12 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6968,24 +7076,24 @@
         </is>
       </c>
       <c r="R7" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>B036-351; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_06.jpg</t>
+          <t>B036-351; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -7023,17 +7131,17 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: children sitting on road map play rug</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -7053,12 +7161,12 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7072,24 +7180,24 @@
         </is>
       </c>
       <c r="R8" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W8" s="2" t="inlineStr"/>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>B036-351; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_07.jpg</t>
+          <t>B036-351; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -7127,17 +7235,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: road map rug material and backing details</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -7157,12 +7265,12 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -7176,24 +7284,24 @@
         </is>
       </c>
       <c r="R9" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>B036-351; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_08.jpg</t>
+          <t>B036-351; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_08.jpg</t>
         </is>
       </c>
     </row>
@@ -7231,17 +7339,17 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: washable road map rug cleaning panel</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -7261,12 +7369,12 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -7280,24 +7388,24 @@
         </is>
       </c>
       <c r="R10" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S10" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>B036-351; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_09.jpg</t>
+          <t>B036-351; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4__img_09.jpg</t>
         </is>
       </c>
     </row>
@@ -7335,17 +7443,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: foggy forest wolf rug beside sofa</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -7365,12 +7473,12 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7384,24 +7492,24 @@
         </is>
       </c>
       <c r="R11" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S11" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>B036-352; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_01.jpg</t>
+          <t>B036-352; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -7439,17 +7547,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: dark wolf rug on wood floor</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -7469,12 +7577,12 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -7488,24 +7596,24 @@
         </is>
       </c>
       <c r="R12" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S12" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>B036-352; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_02.jpg</t>
+          <t>B036-352; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -7543,17 +7651,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: foggy wolf rug in living room</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -7573,12 +7681,12 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7592,24 +7700,24 @@
         </is>
       </c>
       <c r="R13" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S13" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>B036-352; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_03.jpg</t>
+          <t>B036-352; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -7647,17 +7755,17 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: wolf forest rug under sectional sofa</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -7677,12 +7785,12 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7696,24 +7804,24 @@
         </is>
       </c>
       <c r="R14" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S14" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>B036-352; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_04.jpg</t>
+          <t>B036-352; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -7751,17 +7859,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: foggy forest wolf rug under desk</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -7781,12 +7889,12 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -7800,24 +7908,24 @@
         </is>
       </c>
       <c r="R15" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S15" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>B036-352; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_05.jpg</t>
+          <t>B036-352; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -7855,17 +7963,17 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: blue moon wolf lake rug beside sofa</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -7885,12 +7993,12 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7904,24 +8012,24 @@
         </is>
       </c>
       <c r="R16" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S16" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W16" s="2" t="inlineStr"/>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>B036-353; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7__img_01.jpg</t>
+          <t>B036-353; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -7959,17 +8067,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: moonlit wolf rug on wood floor</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -7989,12 +8097,12 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8008,24 +8116,24 @@
         </is>
       </c>
       <c r="R17" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S17" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>B036-353; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7__img_02.jpg</t>
+          <t>B036-353; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -8063,17 +8171,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: wolf lake rug in living room</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -8093,12 +8201,12 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -8112,24 +8220,24 @@
         </is>
       </c>
       <c r="R18" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S18" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W18" s="2" t="inlineStr"/>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>B036-353; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7__img_03.jpg</t>
+          <t>B036-353; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8275,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: blue wolf rug under sectional</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -8197,12 +8305,12 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -8216,24 +8324,24 @@
         </is>
       </c>
       <c r="R19" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S19" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W19" s="2" t="inlineStr"/>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>B036-353; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7__img_04.jpg</t>
+          <t>B036-353; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -8271,17 +8379,17 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: moon wolf rug under desk</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -8301,12 +8409,12 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8320,24 +8428,24 @@
         </is>
       </c>
       <c r="R20" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S20" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>B036-353; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7__img_05.jpg</t>
+          <t>B036-353; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -8375,17 +8483,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: tribal medallion wolf rug beside sofa</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -8405,12 +8513,12 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -8424,24 +8532,24 @@
         </is>
       </c>
       <c r="R21" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S21" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>B036-354; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217__img_01.jpg</t>
+          <t>B036-354; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -8479,17 +8587,17 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: ornate wolf rug on wood floor</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -8509,12 +8617,12 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8528,24 +8636,24 @@
         </is>
       </c>
       <c r="R22" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S22" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W22" s="2" t="inlineStr"/>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>B036-354; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217__img_02.jpg</t>
+          <t>B036-354; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -8583,17 +8691,17 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: tribal wolf rug in living room</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -8613,12 +8721,12 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8632,24 +8740,24 @@
         </is>
       </c>
       <c r="R23" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S23" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T23" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>B036-354; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217__img_03.jpg</t>
+          <t>B036-354; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -8687,17 +8795,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: medallion wolf rug under sectional</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -8717,12 +8825,12 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -8736,24 +8844,24 @@
         </is>
       </c>
       <c r="R24" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S24" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>B036-354; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217__img_04.jpg</t>
+          <t>B036-354; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -8791,17 +8899,17 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: tribal wolf rug under desk</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -8821,12 +8929,12 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -8840,24 +8948,24 @@
         </is>
       </c>
       <c r="R25" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S25" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W25" s="2" t="inlineStr"/>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>B036-354; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217__img_05.jpg</t>
+          <t>B036-354; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -8895,17 +9003,17 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: floral line art wolf rug beside sofa</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -8925,12 +9033,12 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -8944,24 +9052,24 @@
         </is>
       </c>
       <c r="R26" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S26" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W26" s="2" t="inlineStr"/>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>B036-355; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_01.jpg</t>
+          <t>B036-355; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -8999,17 +9107,17 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: botanical wolf rug on wood floor</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -9029,12 +9137,12 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -9048,24 +9156,24 @@
         </is>
       </c>
       <c r="R27" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S27" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T27" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>B036-355; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_02.jpg</t>
+          <t>B036-355; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -9103,17 +9211,17 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: floral wolf rug in living room</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -9133,12 +9241,12 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -9152,24 +9260,24 @@
         </is>
       </c>
       <c r="R28" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S28" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>B036-355; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_03.jpg</t>
+          <t>B036-355; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -9207,17 +9315,17 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: line art wolf rug under sectional</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -9237,12 +9345,12 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -9256,24 +9364,24 @@
         </is>
       </c>
       <c r="R29" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S29" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T29" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>B036-355; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_04.jpg</t>
+          <t>B036-355; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -9311,17 +9419,17 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: floral wolf rug under desk</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -9341,12 +9449,12 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -9360,24 +9468,24 @@
         </is>
       </c>
       <c r="R30" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S30" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W30" s="2" t="inlineStr"/>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>B036-355; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_05.jpg</t>
+          <t>B036-355; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -9415,17 +9523,17 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: sepia wolf pack rug beside sofa</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -9445,12 +9553,12 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -9464,24 +9572,24 @@
         </is>
       </c>
       <c r="R31" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S31" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T31" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W31" s="2" t="inlineStr"/>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>B036-356; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolf-welcome-mat-0e4d706227__img_01.jpg</t>
+          <t>B036-356; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolf-welcome-mat-0e4d706227__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -9519,17 +9627,17 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: wolf pack rug on wood floor</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -9549,12 +9657,12 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -9568,24 +9676,24 @@
         </is>
       </c>
       <c r="R32" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S32" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W32" s="2" t="inlineStr"/>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>B036-356; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolf-welcome-mat-0e4d706227__img_02.jpg</t>
+          <t>B036-356; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolf-welcome-mat-0e4d706227__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -9623,17 +9731,17 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: sepia wolf rug in living room</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -9653,12 +9761,12 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -9672,24 +9780,24 @@
         </is>
       </c>
       <c r="R33" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S33" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T33" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W33" s="2" t="inlineStr"/>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>B036-356; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolf-welcome-mat-0e4d706227__img_03.jpg</t>
+          <t>B036-356; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolf-welcome-mat-0e4d706227__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -9727,17 +9835,17 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: wolf pack rug under sectional sofa</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -9757,12 +9865,12 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -9776,24 +9884,24 @@
         </is>
       </c>
       <c r="R34" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S34" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W34" s="2" t="inlineStr"/>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>B036-356; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolf-welcome-mat-0e4d706227__img_04.jpg</t>
+          <t>B036-356; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolf-welcome-mat-0e4d706227__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -9831,17 +9939,17 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: sepia wolf rug under desk</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -9861,12 +9969,12 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -9880,24 +9988,24 @@
         </is>
       </c>
       <c r="R35" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S35" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T35" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W35" s="2" t="inlineStr"/>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>B036-356; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolf-welcome-mat-0e4d706227__img_05.jpg</t>
+          <t>B036-356; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolf-welcome-mat-0e4d706227__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -9935,17 +10043,17 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: snow close up wolf rug beside sofa</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -9965,12 +10073,12 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -9984,24 +10092,24 @@
         </is>
       </c>
       <c r="R36" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S36" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W36" s="2" t="inlineStr"/>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>B036-357; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9__img_01.jpg</t>
+          <t>B036-357; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -10039,17 +10147,17 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: snowy wolf rug in living room</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -10069,12 +10177,12 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -10088,24 +10196,24 @@
         </is>
       </c>
       <c r="R37" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S37" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T37" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W37" s="2" t="inlineStr"/>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>B036-357; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9__img_02.jpg</t>
+          <t>B036-357; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -10143,17 +10251,17 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: wolf snow rug on wood floor</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -10173,12 +10281,12 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10192,24 +10300,24 @@
         </is>
       </c>
       <c r="R38" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S38" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W38" s="2" t="inlineStr"/>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>B036-357; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9__img_03.jpg</t>
+          <t>B036-357; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -10247,17 +10355,17 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: snow wolf rug under desk</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -10277,12 +10385,12 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -10296,24 +10404,24 @@
         </is>
       </c>
       <c r="R39" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S39" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T39" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W39" s="2" t="inlineStr"/>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>B036-357; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9__img_04.jpg</t>
+          <t>B036-357; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -10351,17 +10459,17 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: close up wolf rug under sectional</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -10381,12 +10489,12 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -10400,24 +10508,24 @@
         </is>
       </c>
       <c r="R40" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S40" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V40" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W40" s="2" t="inlineStr"/>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>B036-357; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9__img_05.jpg</t>
+          <t>B036-357; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -10455,17 +10563,17 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: dreamcatcher wolf rug beside sofa</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -10485,12 +10593,12 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -10504,24 +10612,24 @@
         </is>
       </c>
       <c r="R41" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S41" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T41" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U41" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V41" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W41" s="2" t="inlineStr"/>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>B036-358; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_01.jpg</t>
+          <t>B036-358; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -10559,17 +10667,17 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: wolf dreamcatcher rug on wood floor</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -10589,12 +10697,12 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -10608,24 +10716,24 @@
         </is>
       </c>
       <c r="R42" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S42" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W42" s="2" t="inlineStr"/>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>B036-358; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_02.jpg</t>
+          <t>B036-358; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -10663,17 +10771,17 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: dreamcatcher wolf rug in living room</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -10693,12 +10801,12 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -10712,24 +10820,24 @@
         </is>
       </c>
       <c r="R43" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S43" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T43" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U43" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V43" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W43" s="2" t="inlineStr"/>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>B036-358; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_03.jpg</t>
+          <t>B036-358; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -10767,17 +10875,17 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: wolf area rug under sectional</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -10797,12 +10905,12 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -10816,24 +10924,24 @@
         </is>
       </c>
       <c r="R44" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S44" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T44" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U44" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V44" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W44" s="2" t="inlineStr"/>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>B036-358; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_04.jpg</t>
+          <t>B036-358; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -10871,17 +10979,17 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: dreamcatcher wolf rug under desk</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -10901,12 +11009,12 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -10920,24 +11028,24 @@
         </is>
       </c>
       <c r="R45" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S45" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T45" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V45" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W45" s="2" t="inlineStr"/>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>B036-358; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_05.jpg</t>
+          <t>B036-358; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -10975,17 +11083,17 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: blue moon mountain wolf rug beside sofa</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -11005,12 +11113,12 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -11024,24 +11132,24 @@
         </is>
       </c>
       <c r="R46" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S46" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T46" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U46" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V46" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W46" s="2" t="inlineStr"/>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>B036-359; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-e0ded989b1__img_01.jpg</t>
+          <t>B036-359; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-e0ded989b1__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -11079,17 +11187,17 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: howling wolf rug on wood floor</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -11109,12 +11217,12 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -11128,24 +11236,24 @@
         </is>
       </c>
       <c r="R47" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S47" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T47" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U47" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V47" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W47" s="2" t="inlineStr"/>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>B036-359; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-e0ded989b1__img_02.jpg</t>
+          <t>B036-359; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-e0ded989b1__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -11183,17 +11291,17 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: moon mountain wolf rug in living room</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -11213,12 +11321,12 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -11232,24 +11340,24 @@
         </is>
       </c>
       <c r="R48" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S48" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T48" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U48" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V48" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W48" s="2" t="inlineStr"/>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>B036-359; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-e0ded989b1__img_03.jpg</t>
+          <t>B036-359; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-e0ded989b1__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -11287,17 +11395,17 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: blue wolf rug under sectional</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -11317,12 +11425,12 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -11336,24 +11444,24 @@
         </is>
       </c>
       <c r="R49" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S49" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T49" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U49" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V49" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W49" s="2" t="inlineStr"/>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>B036-359; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-e0ded989b1__img_04.jpg</t>
+          <t>B036-359; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-e0ded989b1__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -11391,17 +11499,17 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: howling wolf rug under desk</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -11421,12 +11529,12 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -11440,24 +11548,24 @@
         </is>
       </c>
       <c r="R50" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S50" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T50" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U50" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V50" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W50" s="2" t="inlineStr"/>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>B036-359; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-e0ded989b1__img_05.jpg</t>
+          <t>B036-359; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/custom-galaxy-wolves-rug-boy-room-e0ded989b1__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -11495,17 +11603,17 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: two tone galaxy wolf rug beside sofa</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -11525,12 +11633,12 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -11544,24 +11652,24 @@
         </is>
       </c>
       <c r="R51" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S51" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T51" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U51" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V51" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W51" s="2" t="inlineStr"/>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>B036-360; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_01.jpg</t>
+          <t>B036-360; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -11599,17 +11707,17 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: pink blue wolf rug on wood floor</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -11629,12 +11737,12 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -11648,24 +11756,24 @@
         </is>
       </c>
       <c r="R52" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S52" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T52" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U52" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V52" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W52" s="2" t="inlineStr"/>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>B036-360; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_02.jpg</t>
+          <t>B036-360; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -11703,17 +11811,17 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: galaxy wolf rug in living room</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -11733,12 +11841,12 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -11752,24 +11860,24 @@
         </is>
       </c>
       <c r="R53" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S53" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T53" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U53" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V53" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W53" s="2" t="inlineStr"/>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>B036-360; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_03.jpg</t>
+          <t>B036-360; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -11807,17 +11915,17 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: two tone wolf rug under sectional</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -11837,12 +11945,12 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -11856,24 +11964,24 @@
         </is>
       </c>
       <c r="R54" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S54" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T54" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U54" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V54" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W54" s="2" t="inlineStr"/>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>B036-360; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_04.jpg</t>
+          <t>B036-360; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -11911,17 +12019,17 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:56:21.258646+00:00</t>
+          <t>2026-09-07T16:54:10.826810+00:00</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: galaxy wolf rug under desk</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -11941,12 +12049,12 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -11960,24 +12068,24 @@
         </is>
       </c>
       <c r="R55" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S55" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T55" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U55" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V55" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W55" s="2" t="inlineStr"/>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>B036-360; local B036 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_05.jpg</t>
+          <t>B036-360; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B036/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12236,7 +12344,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4</t>
+          <t>chillgen.com::custom-road-map-area-rug-81bfb9cda4-81bfb9cda4</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -12247,196 +12355,180 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
-        </is>
-      </c>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B036 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; B036-352</t>
+          <t>https://chillgen.com/products/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4; B036-351</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>LIM-0004</t>
+          <t>AUTO-0004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4</t>
+          <t>chillgen.com::custom-road-map-area-rug-81bfb9cda4-81bfb9cda4</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>LIMITATION</t>
+          <t>MAJOR</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>foggy forest wolf rug</t>
-        </is>
-      </c>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+          <t>Remove unsupported claims or add source evidence.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/childrens-road-rug/s?k=childrens+road+rug; https://www.walmart.com/c/kp/kids-road-map-rug; https://www.etsy.com/market/kids_rug_town; https://ruggable.com/collections/kids-rugs; https://www.walmart.com/c/kp/wolf-rugs; https://www.etsy.com/listing/1103907014/galaxy-area-rug-non-slip-universe-carpet; https://chillgen.com/</t>
+          <t>https://chillgen.com/products/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4; B036-351</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>Field passes evidence-driven QA rule.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LIM-0005</t>
+          <t>AUTO-0005</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7</t>
+          <t>chillgen.com::custom-road-map-area-rug-81bfb9cda4-81bfb9cda4</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>LIMITATION</t>
+          <t>MAJOR</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
-        </is>
-      </c>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B036 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>Title length 24 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>Title length 24 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>Revise this field and re-QA.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7; B036-353</t>
+          <t>https://chillgen.com/products/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4; B036-351</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>Field passes evidence-driven QA rule.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>LIM-0006</t>
+          <t>AUTO-0006</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7</t>
+          <t>chillgen.com::custom-road-map-area-rug-81bfb9cda4-81bfb9cda4</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>LIMITATION</t>
+          <t>MAJOR</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>blue moon wolf lake rug</t>
-        </is>
-      </c>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>Title length 24 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>Title length 24 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+          <t>Revise this field and re-QA.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/childrens-road-rug/s?k=childrens+road+rug; https://www.walmart.com/c/kp/kids-road-map-rug; https://www.etsy.com/market/kids_rug_town; https://ruggable.com/collections/kids-rugs; https://www.walmart.com/c/kp/wolf-rugs; https://www.etsy.com/listing/1103907014/galaxy-area-rug-non-slip-universe-carpet; https://chillgen.com/</t>
+          <t>https://chillgen.com/products/custom-road-map-area-rug-81bfb9cda4-81bfb9cda4; B036-351</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>Field passes evidence-driven QA rule.</t>
         </is>
       </c>
     </row>
@@ -12448,7 +12540,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217</t>
+          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
@@ -12484,7 +12576,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217; B036-354</t>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; B036-352</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -12501,7 +12593,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217</t>
+          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
@@ -12517,7 +12609,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>tribal medallion wolf rug</t>
+          <t>foggy forest wolf rug</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12554,7 +12646,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17</t>
+          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
@@ -12565,196 +12657,180 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
-        </is>
-      </c>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B036 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; B036-355</t>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; B036-352</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>LIM-0010</t>
+          <t>AUTO-0010</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17</t>
+          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>LIMITATION</t>
+          <t>MAJOR</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>floral line art wolf rug</t>
-        </is>
-      </c>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+          <t>Remove unsupported claims or add source evidence.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/childrens-road-rug/s?k=childrens+road+rug; https://www.walmart.com/c/kp/kids-road-map-rug; https://www.etsy.com/market/kids_rug_town; https://ruggable.com/collections/kids-rugs; https://www.walmart.com/c/kp/wolf-rugs; https://www.etsy.com/listing/1103907014/galaxy-area-rug-non-slip-universe-carpet; https://chillgen.com/</t>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; B036-352</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>Field passes evidence-driven QA rule.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>LIM-0011</t>
+          <t>AUTO-0011</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-galaxy-wolf-welcome-mat-0e4d706227</t>
+          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>LIMITATION</t>
+          <t>MAJOR</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
-        </is>
-      </c>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B036 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>Title length 21 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>Title length 21 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>Revise this field and re-QA.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; B036-356</t>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; B036-352</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>Field passes evidence-driven QA rule.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LIM-0012</t>
+          <t>AUTO-0012</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-galaxy-wolf-welcome-mat-0e4d706227</t>
+          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>LIMITATION</t>
+          <t>MAJOR</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>sepia wolf pack rug</t>
-        </is>
-      </c>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>Title length 21 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>Title length 21 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+          <t>Revise this field and re-QA.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/childrens-road-rug/s?k=childrens+road+rug; https://www.walmart.com/c/kp/kids-road-map-rug; https://www.etsy.com/market/kids_rug_town; https://ruggable.com/collections/kids-rugs; https://www.walmart.com/c/kp/wolf-rugs; https://www.etsy.com/listing/1103907014/galaxy-area-rug-non-slip-universe-carpet; https://chillgen.com/</t>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-bedroom-167aea55b4; B036-352</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>Field passes evidence-driven QA rule.</t>
         </is>
       </c>
     </row>
@@ -12766,7 +12842,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9</t>
+          <t>chillgen.com::galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
@@ -12802,7 +12878,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9; B036-357</t>
+          <t>https://chillgen.com/products/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7; B036-353</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -12819,7 +12895,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9</t>
+          <t>chillgen.com::galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
@@ -12835,7 +12911,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>snow close up wolf rug</t>
+          <t>blue moon wolf lake rug</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12872,7 +12948,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e</t>
+          <t>chillgen.com::galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -12883,196 +12959,180 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
-        </is>
-      </c>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B036 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; B036-358</t>
+          <t>https://chillgen.com/products/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7; B036-353</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LIM-0016</t>
+          <t>AUTO-0016</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e</t>
+          <t>chillgen.com::galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>LIMITATION</t>
+          <t>MAJOR</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>dreamcatcher wolf rug</t>
-        </is>
-      </c>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+          <t>Remove unsupported claims or add source evidence.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/childrens-road-rug/s?k=childrens+road+rug; https://www.walmart.com/c/kp/kids-road-map-rug; https://www.etsy.com/market/kids_rug_town; https://ruggable.com/collections/kids-rugs; https://www.walmart.com/c/kp/wolf-rugs; https://www.etsy.com/listing/1103907014/galaxy-area-rug-non-slip-universe-carpet; https://chillgen.com/</t>
+          <t>https://chillgen.com/products/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7; B036-353</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>Field passes evidence-driven QA rule.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>LIM-0017</t>
+          <t>AUTO-0017</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-e0ded989b1</t>
+          <t>chillgen.com::galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>LIMITATION</t>
+          <t>MAJOR</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
-        </is>
-      </c>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B036 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>Title length 23 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>Title length 23 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>Revise this field and re-QA.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-e0ded989b1; B036-359</t>
+          <t>https://chillgen.com/products/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7; B036-353</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>Field passes evidence-driven QA rule.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>LIM-0018</t>
+          <t>AUTO-0018</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-e0ded989b1</t>
+          <t>chillgen.com::galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>LIMITATION</t>
+          <t>MAJOR</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>blue moon mountain wolf rug</t>
-        </is>
-      </c>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>Title length 23 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>Title length 23 is outside practical SEO/title range.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+          <t>Revise this field and re-QA.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/childrens-road-rug/s?k=childrens+road+rug; https://www.walmart.com/c/kp/kids-road-map-rug; https://www.etsy.com/market/kids_rug_town; https://ruggable.com/collections/kids-rugs; https://www.walmart.com/c/kp/wolf-rugs; https://www.etsy.com/listing/1103907014/galaxy-area-rug-non-slip-universe-carpet; https://chillgen.com/</t>
+          <t>https://chillgen.com/products/galaxy-wolves-wild-wolf-print-area-rug-c951e785f7-c951e785f7; B036-353</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>Field passes evidence-driven QA rule.</t>
         </is>
       </c>
     </row>
@@ -13084,7 +13144,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e</t>
+          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
@@ -13120,7 +13180,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; B036-360</t>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217; B036-354</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -13137,7 +13197,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e</t>
+          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
@@ -13153,37 +13213,1849 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>tribal medallion wolf rug</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/childrens-road-rug/s?k=childrens+road+rug; https://www.walmart.com/c/kp/kids-road-map-rug; https://www.etsy.com/market/kids_rug_town; https://ruggable.com/collections/kids-rugs; https://www.walmart.com/c/kp/wolf-rugs; https://www.etsy.com/listing/1103907014/galaxy-area-rug-non-slip-universe-carpet; https://chillgen.com/</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217; B036-354</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-a0375b4217-a0375b4217; B036-354</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>admin_identity_and_admin_seo_fields</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B036 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; B036-355</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>keyword_demand_evidence</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>floral line art wolf rug</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/childrens-road-rug/s?k=childrens+road+rug; https://www.walmart.com/c/kp/kids-road-map-rug; https://www.etsy.com/market/kids_rug_town; https://ruggable.com/collections/kids-rugs; https://www.walmart.com/c/kp/wolf-rugs; https://www.etsy.com/listing/1103907014/galaxy-area-rug-non-slip-universe-carpet; https://chillgen.com/</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; B036-355</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; B036-355</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Title length 24 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Title length 24 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Revise this field and re-QA.</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; B036-355</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Title length 24 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Title length 24 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Revise this field and re-QA.</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/galaxy-wolves-wolf-area-rug-94b47adf17-94b47adf17; B036-355</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolf-welcome-mat-0e4d706227</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>admin_identity_and_admin_seo_fields</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B036 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; B036-356</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolf-welcome-mat-0e4d706227</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>keyword_demand_evidence</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>sepia wolf pack rug</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/childrens-road-rug/s?k=childrens+road+rug; https://www.walmart.com/c/kp/kids-road-map-rug; https://www.etsy.com/market/kids_rug_town; https://ruggable.com/collections/kids-rugs; https://www.walmart.com/c/kp/wolf-rugs; https://www.etsy.com/listing/1103907014/galaxy-area-rug-non-slip-universe-carpet; https://chillgen.com/</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolf-welcome-mat-0e4d706227</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; B036-356</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolf-welcome-mat-0e4d706227</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; B036-356</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolf-welcome-mat-0e4d706227</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Title length 19 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Title length 19 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Revise this field and re-QA.</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; B036-356</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolf-welcome-mat-0e4d706227</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Title length 19 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Title length 19 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Revise this field and re-QA.</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolf-welcome-mat-0e4d706227; B036-356</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>admin_identity_and_admin_seo_fields</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B036 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9; B036-357</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>keyword_demand_evidence</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>snow close up wolf rug</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/childrens-road-rug/s?k=childrens+road+rug; https://www.walmart.com/c/kp/kids-road-map-rug; https://www.etsy.com/market/kids_rug_town; https://ruggable.com/collections/kids-rugs; https://www.walmart.com/c/kp/wolf-rugs; https://www.etsy.com/listing/1103907014/galaxy-area-rug-non-slip-universe-carpet; https://chillgen.com/</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9; B036-357</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9; B036-357</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Title length 22 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Title length 22 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Revise this field and re-QA.</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9; B036-357</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Title length 22 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Title length 22 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Revise this field and re-QA.</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-welcome-mat-5ce46e57d9-5ce46e57d9; B036-357</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>admin_identity_and_admin_seo_fields</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B036 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; B036-358</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>keyword_demand_evidence</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>dreamcatcher wolf rug</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/childrens-road-rug/s?k=childrens+road+rug; https://www.walmart.com/c/kp/kids-road-map-rug; https://www.etsy.com/market/kids_rug_town; https://ruggable.com/collections/kids-rugs; https://www.walmart.com/c/kp/wolf-rugs; https://www.etsy.com/listing/1103907014/galaxy-area-rug-non-slip-universe-carpet; https://chillgen.com/</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; B036-358</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0044</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; B036-358</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0045</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Title length 21 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Title length 21 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Revise this field and re-QA.</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; B036-358</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0046</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Title length 21 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Title length 21 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Revise this field and re-QA.</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/galaxy-wolves-wolf-area-rug-carpet-da377ca92e-da377ca92e; B036-358</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0047</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-e0ded989b1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>admin_identity_and_admin_seo_fields</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B036 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-e0ded989b1; B036-359</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0048</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-e0ded989b1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>keyword_demand_evidence</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>blue moon mountain wolf rug</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/childrens-road-rug/s?k=childrens+road+rug; https://www.walmart.com/c/kp/kids-road-map-rug; https://www.etsy.com/market/kids_rug_town; https://ruggable.com/collections/kids-rugs; https://www.walmart.com/c/kp/wolf-rugs; https://www.etsy.com/listing/1103907014/galaxy-area-rug-non-slip-universe-carpet; https://chillgen.com/</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0049</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-e0ded989b1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-e0ded989b1; B036-359</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0050</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-galaxy-wolves-rug-boy-room-e0ded989b1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-galaxy-wolves-rug-boy-room-e0ded989b1; B036-359</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0051</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>admin_identity_and_admin_seo_fields</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B036 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; B036-360</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0052</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>keyword_demand_evidence</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>two tone galaxy wolf rug</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>https://www.amazon.com/childrens-road-rug/s?k=childrens+road+rug; https://www.walmart.com/c/kp/kids-road-map-rug; https://www.etsy.com/market/kids_rug_town; https://ruggable.com/collections/kids-rugs; https://www.walmart.com/c/kp/wolf-rugs; https://www.etsy.com/listing/1103907014/galaxy-area-rug-non-slip-universe-carpet; https://chillgen.com/</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0053</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; B036-360</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0054</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; B036-360</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0055</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Title length 24 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Title length 24 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Revise this field and re-QA.</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; B036-360</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0056</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Title length 24 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Title length 24 is outside practical SEO/title range.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Revise this field and re-QA.</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/wolf-galaxy-wolves-area-rug-f49c8f2c6e-f49c8f2c6e; B036-360</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K21"/>
+  <autoFilter ref="A1:K57"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
@@ -13205,6 +15077,42 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
